--- a/output/sales_report.xlsx
+++ b/output/sales_report.xlsx
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1340</v>
+        <v>890</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15/03/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">

--- a/output/sales_report.xlsx
+++ b/output/sales_report.xlsx
@@ -32,12 +32,30 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0066FF33"/>
+        <bgColor rgb="0066FF33"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -58,11 +76,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -137,6 +158,58 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_Resume" displayName="Table_Resume" ref="A1:B6" headerRowCount="1">
+  <autoFilter ref="A1:B6"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="metric"/>
+    <tableColumn id="2" name="quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_Top_products" displayName="Table_Top_products" ref="A1:G7" headerRowCount="1">
+  <autoFilter ref="A1:G7"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="product"/>
+    <tableColumn id="2" name="total_profit"/>
+    <tableColumn id="3" name="quantity"/>
+    <tableColumn id="4" name="total_cost"/>
+    <tableColumn id="5" name="total_income"/>
+    <tableColumn id="6" name="individual_cost"/>
+    <tableColumn id="7" name="individual_price"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table_Daily_sales" displayName="Table_Daily_sales" ref="A1:C29" headerRowCount="1">
+  <autoFilter ref="A1:C29"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="date"/>
+    <tableColumn id="2" name="revenue"/>
+    <tableColumn id="3" name="number_of_sales"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table_Merged_Data" displayName="Table_Merged_Data" ref="A1:D94" headerRowCount="1">
+  <autoFilter ref="A1:D94"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="order_id"/>
+    <tableColumn id="2" name="date"/>
+    <tableColumn id="3" name="product"/>
+    <tableColumn id="4" name="quantity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -431,8 +504,8 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,7 +527,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="3">
@@ -464,7 +537,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>11335</v>
       </c>
     </row>
     <row r="4">
@@ -474,7 +547,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>19335</v>
       </c>
     </row>
     <row r="5">
@@ -494,11 +567,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>207.9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -511,13 +587,13 @@
   <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,155 +636,208 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hoodie</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
+        <v>2145</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>143</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2860</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>5005</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
+        <v>1920</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2880</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sneakers</t>
+          <t>Hoodie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
+        <v>1420</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>142</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3550</v>
       </c>
       <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
         <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>Sneakers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
+        <v>1260</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>84</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
+        <v>770</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Cap</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
+        <v>485</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>97</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:B7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0066FF33"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D7">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0066FF33"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E7">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0066FF33"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F7">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0066FF33"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00FFFF00"/>
+        <color rgb="0066FF33"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -721,9 +850,9 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,7 +881,7 @@
       <c r="B2" t="n">
         <v>335</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -765,7 +894,7 @@
       <c r="B3" t="n">
         <v>475</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -778,7 +907,7 @@
       <c r="B4" t="n">
         <v>360</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -791,7 +920,7 @@
       <c r="B5" t="n">
         <v>620</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -804,7 +933,7 @@
       <c r="B6" t="n">
         <v>405</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -817,7 +946,7 @@
       <c r="B7" t="n">
         <v>385</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -830,7 +959,7 @@
       <c r="B8" t="n">
         <v>125</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -843,7 +972,7 @@
       <c r="B9" t="n">
         <v>700</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -856,7 +985,7 @@
       <c r="B10" t="n">
         <v>700</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -869,7 +998,7 @@
       <c r="B11" t="n">
         <v>335</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -882,7 +1011,7 @@
       <c r="B12" t="n">
         <v>600</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -895,7 +1024,7 @@
       <c r="B13" t="n">
         <v>375</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -908,7 +1037,7 @@
       <c r="B14" t="n">
         <v>40</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -921,7 +1050,7 @@
       <c r="B15" t="n">
         <v>515</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -934,7 +1063,7 @@
       <c r="B16" t="n">
         <v>890</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -947,7 +1076,7 @@
       <c r="B17" t="n">
         <v>815</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -960,7 +1089,7 @@
       <c r="B18" t="n">
         <v>785</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -973,7 +1102,7 @@
       <c r="B19" t="n">
         <v>800</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -986,7 +1115,7 @@
       <c r="B20" t="n">
         <v>875</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -999,7 +1128,7 @@
       <c r="B21" t="n">
         <v>500</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1012,7 +1141,7 @@
       <c r="B22" t="n">
         <v>455</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1025,7 +1154,7 @@
       <c r="B23" t="n">
         <v>1380</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1038,7 +1167,7 @@
       <c r="B24" t="n">
         <v>460</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1051,7 +1180,7 @@
       <c r="B25" t="n">
         <v>1605</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1064,7 +1193,7 @@
       <c r="B26" t="n">
         <v>1205</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1077,7 +1206,7 @@
       <c r="B27" t="n">
         <v>1130</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1090,7 +1219,7 @@
       <c r="B28" t="n">
         <v>1250</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1103,12 +1232,15 @@
       <c r="B29" t="n">
         <v>1215</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="2" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1121,10 +1253,10 @@
   <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1163,7 +1295,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1181,7 +1313,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1199,7 +1331,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1217,7 +1349,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1235,7 +1367,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1253,7 +1385,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1271,7 +1403,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1289,7 +1421,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1307,7 +1439,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1325,7 +1457,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1343,7 +1475,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1361,7 +1493,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1379,7 +1511,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1397,7 +1529,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1415,7 +1547,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1433,7 +1565,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1451,7 +1583,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1469,7 +1601,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1487,7 +1619,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1505,7 +1637,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1523,7 +1655,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1541,7 +1673,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1559,7 +1691,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1577,7 +1709,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1595,7 +1727,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1613,7 +1745,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1631,7 +1763,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1649,7 +1781,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1667,7 +1799,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1685,7 +1817,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1703,7 +1835,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1721,7 +1853,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1739,7 +1871,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1757,7 +1889,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1775,7 +1907,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1793,7 +1925,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1811,7 +1943,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1829,7 +1961,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1847,7 +1979,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1865,7 +1997,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1883,7 +2015,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1901,7 +2033,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1919,7 +2051,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1937,7 +2069,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1955,7 +2087,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1973,7 +2105,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1991,7 +2123,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2009,7 +2141,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2027,7 +2159,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2045,7 +2177,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2063,7 +2195,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2081,7 +2213,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2099,7 +2231,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2117,7 +2249,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2135,7 +2267,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2153,7 +2285,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2171,7 +2303,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2189,7 +2321,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2207,7 +2339,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2225,7 +2357,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2243,7 +2375,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2261,7 +2393,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2279,7 +2411,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2297,7 +2429,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2315,7 +2447,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2333,7 +2465,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2351,7 +2483,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2369,7 +2501,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2387,7 +2519,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2405,7 +2537,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2423,7 +2555,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2441,7 +2573,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2459,7 +2591,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2477,7 +2609,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2495,7 +2627,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2513,7 +2645,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="2" t="n">
         <v>16</v>
       </c>
     </row>
@@ -2531,7 +2663,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2549,7 +2681,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2567,7 +2699,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2585,7 +2717,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="2" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2603,7 +2735,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2621,7 +2753,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2639,7 +2771,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2657,7 +2789,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2675,7 +2807,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2693,7 +2825,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2711,7 +2843,7 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2729,7 +2861,7 @@
           <t>Hoodie</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2747,7 +2879,7 @@
           <t>Cap</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2765,7 +2897,7 @@
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="3" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2783,7 +2915,7 @@
           <t>Jacket</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2801,7 +2933,7 @@
           <t>T-shirt</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="3" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2819,11 +2951,14 @@
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="3" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>